--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>934.278</v>
+        <v>957.677</v>
       </c>
       <c r="D2">
-        <v>66.71299999999999</v>
+        <v>64.759</v>
       </c>
       <c r="E2">
-        <v>8.167999999999999</v>
+        <v>8.047000000000001</v>
       </c>
       <c r="F2">
-        <v>0.258</v>
+        <v>0.254</v>
       </c>
       <c r="G2">
-        <v>918.173</v>
+        <v>941.826</v>
       </c>
       <c r="H2">
-        <v>950.1900000000001</v>
+        <v>973.371</v>
       </c>
       <c r="I2">
-        <v>918.351</v>
+        <v>942.371</v>
       </c>
       <c r="J2">
-        <v>950.254</v>
+        <v>973.7619999999999</v>
       </c>
       <c r="K2">
-        <v>918.206</v>
+        <v>941.514</v>
       </c>
       <c r="L2">
-        <v>950.1079999999999</v>
+        <v>972.905</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>266.756</v>
+        <v>441.863</v>
       </c>
       <c r="D3">
-        <v>25.298</v>
+        <v>57.262</v>
       </c>
       <c r="E3">
-        <v>5.03</v>
+        <v>7.567</v>
       </c>
       <c r="F3">
-        <v>0.159</v>
+        <v>0.239</v>
       </c>
       <c r="G3">
-        <v>256.896</v>
+        <v>426.893</v>
       </c>
       <c r="H3">
-        <v>276.612</v>
+        <v>456.556</v>
       </c>
       <c r="I3">
-        <v>257.04</v>
+        <v>426.811</v>
       </c>
       <c r="J3">
-        <v>276.586</v>
+        <v>456.829</v>
       </c>
       <c r="K3">
-        <v>256.924</v>
+        <v>426.759</v>
       </c>
       <c r="L3">
-        <v>276.469</v>
+        <v>456.777</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1043.239</v>
+        <v>1069.4</v>
       </c>
       <c r="D4">
-        <v>76.798</v>
+        <v>75.244</v>
       </c>
       <c r="E4">
-        <v>8.763</v>
+        <v>8.673999999999999</v>
       </c>
       <c r="F4">
-        <v>0.277</v>
+        <v>0.274</v>
       </c>
       <c r="G4">
-        <v>1026.125</v>
+        <v>1052.42</v>
       </c>
       <c r="H4">
-        <v>1060.477</v>
+        <v>1086.423</v>
       </c>
       <c r="I4">
-        <v>1026.416</v>
+        <v>1053.044</v>
       </c>
       <c r="J4">
-        <v>1060.864</v>
+        <v>1087.035</v>
       </c>
       <c r="K4">
-        <v>1025.676</v>
+        <v>1051.787</v>
       </c>
       <c r="L4">
-        <v>1060.125</v>
+        <v>1085.778</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>297.786</v>
+        <v>472.763</v>
       </c>
       <c r="D5">
-        <v>30.341</v>
+        <v>62.665</v>
       </c>
       <c r="E5">
-        <v>5.508</v>
+        <v>7.916</v>
       </c>
       <c r="F5">
-        <v>0.174</v>
+        <v>0.25</v>
       </c>
       <c r="G5">
-        <v>287.197</v>
+        <v>457.479</v>
       </c>
       <c r="H5">
-        <v>308.789</v>
+        <v>488.509</v>
       </c>
       <c r="I5">
-        <v>287.29</v>
+        <v>456.829</v>
       </c>
       <c r="J5">
-        <v>308.797</v>
+        <v>488.552</v>
       </c>
       <c r="K5">
-        <v>286.982</v>
+        <v>457.204</v>
       </c>
       <c r="L5">
-        <v>308.489</v>
+        <v>488.928</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>957.677</v>
+        <v>966.088</v>
       </c>
       <c r="D2">
-        <v>64.759</v>
+        <v>68.02800000000001</v>
       </c>
       <c r="E2">
-        <v>8.047000000000001</v>
+        <v>8.247999999999999</v>
       </c>
       <c r="F2">
-        <v>0.254</v>
+        <v>0.261</v>
       </c>
       <c r="G2">
-        <v>941.826</v>
+        <v>949.808</v>
       </c>
       <c r="H2">
-        <v>973.371</v>
+        <v>982.139</v>
       </c>
       <c r="I2">
-        <v>942.371</v>
+        <v>950.6609999999999</v>
       </c>
       <c r="J2">
-        <v>973.7619999999999</v>
+        <v>982.582</v>
       </c>
       <c r="K2">
-        <v>941.514</v>
+        <v>949.48</v>
       </c>
       <c r="L2">
-        <v>972.905</v>
+        <v>981.401</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>441.863</v>
+        <v>425.084</v>
       </c>
       <c r="D3">
-        <v>57.262</v>
+        <v>51.89</v>
       </c>
       <c r="E3">
-        <v>7.567</v>
+        <v>7.203</v>
       </c>
       <c r="F3">
-        <v>0.239</v>
+        <v>0.228</v>
       </c>
       <c r="G3">
-        <v>426.893</v>
+        <v>410.984</v>
       </c>
       <c r="H3">
-        <v>456.556</v>
+        <v>439.221</v>
       </c>
       <c r="I3">
-        <v>426.811</v>
+        <v>410.749</v>
       </c>
       <c r="J3">
-        <v>456.829</v>
+        <v>439.276</v>
       </c>
       <c r="K3">
-        <v>426.759</v>
+        <v>410.91</v>
       </c>
       <c r="L3">
-        <v>456.777</v>
+        <v>439.437</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1069.4</v>
+        <v>1078.701</v>
       </c>
       <c r="D4">
-        <v>75.244</v>
+        <v>80.61199999999999</v>
       </c>
       <c r="E4">
-        <v>8.673999999999999</v>
+        <v>8.978</v>
       </c>
       <c r="F4">
-        <v>0.274</v>
+        <v>0.284</v>
       </c>
       <c r="G4">
-        <v>1052.42</v>
+        <v>1061.269</v>
       </c>
       <c r="H4">
-        <v>1086.423</v>
+        <v>1096.464</v>
       </c>
       <c r="I4">
-        <v>1053.044</v>
+        <v>1060.479</v>
       </c>
       <c r="J4">
-        <v>1087.035</v>
+        <v>1096.704</v>
       </c>
       <c r="K4">
-        <v>1051.787</v>
+        <v>1060.864</v>
       </c>
       <c r="L4">
-        <v>1085.778</v>
+        <v>1097.088</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>472.763</v>
+        <v>454.994</v>
       </c>
       <c r="D5">
-        <v>62.665</v>
+        <v>58.455</v>
       </c>
       <c r="E5">
-        <v>7.916</v>
+        <v>7.646</v>
       </c>
       <c r="F5">
-        <v>0.25</v>
+        <v>0.242</v>
       </c>
       <c r="G5">
-        <v>457.479</v>
+        <v>440.025</v>
       </c>
       <c r="H5">
-        <v>488.509</v>
+        <v>469.995</v>
       </c>
       <c r="I5">
-        <v>456.829</v>
+        <v>440.043</v>
       </c>
       <c r="J5">
-        <v>488.552</v>
+        <v>469.737</v>
       </c>
       <c r="K5">
-        <v>457.204</v>
+        <v>440.268</v>
       </c>
       <c r="L5">
-        <v>488.928</v>
+        <v>469.962</v>
       </c>
     </row>
   </sheetData>
